--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,56 +912,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104075058</v>
+        <v>137080259</v>
       </c>
       <c r="B4" t="n">
-        <v>97986</v>
+        <v>58169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vapnö mosse mot O, Hl</t>
+          <t>Vändplatsen ca 400 m VSV om Äspelundsåsen, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>371977</v>
+        <v>371982</v>
       </c>
       <c r="R4" t="n">
-        <v>6293958</v>
+        <v>6294597</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,82 +1013,76 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>granåker stig</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Uno Unger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104075058</t>
+          <t>https://artportalen.se/Sighting/137080259</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102135799</v>
+        <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>98194</v>
+        <v>107554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220686</v>
+        <v>221647</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Galeopsis ladanum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Högabjär, vägdike väster om, Hl</t>
+          <t>Vändplatsen ca 400 m VSV om Äspelundsåsen, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>371673</v>
+        <v>371982</v>
       </c>
       <c r="R5" t="n">
-        <v>6292812</v>
+        <v>6294597</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,12 +1109,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-08</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-08</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Åtminstone några stjälkar i blom.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,27 +1145,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Stibe</t>
+          <t>Uno Unger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Stibe</t>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102135799</t>
+          <t>https://artportalen.se/Sighting/137078080</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110540051</v>
+        <v>104075058</v>
       </c>
       <c r="B6" t="n">
-        <v>98194</v>
+        <v>97986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,38 +1173,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220686</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Högabjär V, Hl</t>
+          <t>Vapnö mosse mot O, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>371666</v>
+        <v>371977</v>
       </c>
       <c r="R6" t="n">
-        <v>6292773</v>
+        <v>6293958</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1208,12 +1235,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,27 +1253,32 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>granåker stig</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kirsten Malmström</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kirsten Malmström, Lars Stibe, Per Wahlén</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110540051</t>
+          <t>https://artportalen.se/Sighting/104075058</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115160472</v>
+        <v>102135799</v>
       </c>
       <c r="B7" t="n">
         <v>98194</v>
@@ -1285,17 +1317,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Högabjär mot V, Hl</t>
+          <t>Högabjär, vägdike väster om, Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>371691</v>
+        <v>371673</v>
       </c>
       <c r="R7" t="n">
-        <v>6292824</v>
+        <v>6292812</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,12 +1351,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,81 +1369,72 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bäck</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Lars Stibe</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Lars Stibe</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115160472</t>
+          <t>https://artportalen.se/Sighting/102135799</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135224675</v>
+        <v>110540051</v>
       </c>
       <c r="B8" t="n">
-        <v>99804</v>
+        <v>98194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222541</v>
+        <v>220686</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Juncus squarrosus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vapnö mosse, Hl</t>
+          <t>Högabjär V, Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372350</v>
+        <v>371666</v>
       </c>
       <c r="R8" t="n">
-        <v>6293104</v>
+        <v>6292773</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,12 +1458,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,35 +1476,30 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Skogsvägkant</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Kirsten Malmström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Kirsten Malmström, Lars Stibe, Per Wahlén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135224675</t>
+          <t>https://artportalen.se/Sighting/110540051</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110539372</v>
+        <v>115160472</v>
       </c>
       <c r="B9" t="n">
-        <v>97987</v>
+        <v>98194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,37 +1507,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224364</v>
+        <v>220686</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>V  Vapnö mosse, Hl</t>
+          <t>Högabjär mot V, Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372360</v>
+        <v>371691</v>
       </c>
       <c r="R9" t="n">
-        <v>6292992</v>
+        <v>6292824</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,12 +1569,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,69 +1587,78 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kirsten Malmström</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kirsten Malmström, Lars Stibe, Per Wahlén</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110539372</t>
+          <t>https://artportalen.se/Sighting/115160472</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126634310</v>
+        <v>135224675</v>
       </c>
       <c r="B10" t="n">
-        <v>97987</v>
+        <v>99804</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224364</v>
+        <v>222541</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Juncus squarrosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vapnö mosse, stig, Hl</t>
+          <t>Vapnö mosse, Hl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372369</v>
+        <v>372350</v>
       </c>
       <c r="R10" t="n">
-        <v>6293017</v>
+        <v>6293104</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,12 +1685,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,30 +1703,35 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Skogsvägkant</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Stibe</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Stibe</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126634310</t>
+          <t>https://artportalen.se/Sighting/135224675</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135224633</v>
+        <v>110539372</v>
       </c>
       <c r="B11" t="n">
-        <v>98142</v>
+        <v>97987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,23 +1754,19 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vapnö mosse, Hl</t>
+          <t>V  Vapnö mosse, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372368</v>
+        <v>372360</v>
       </c>
       <c r="R11" t="n">
-        <v>6292986</v>
+        <v>6292992</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,17 +1793,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikliga mängder</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,24 +1811,243 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Skogsvägkant hygge</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Kirsten Malmström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Kirsten Malmström, Lars Stibe, Per Wahlén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110539372</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126634310</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vapnö mosse, stig, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>372369</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6293017</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Stibe</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Stibe</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126634310</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135224633</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vapnö mosse, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>372368</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6292986</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikliga mängder</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Skogsvägkant hygge</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135224633</t>
         </is>
@@ -1815,6 +2065,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107554</v>
+        <v>107555</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107555</v>
+        <v>107561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107561</v>
+        <v>107565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107565</v>
+        <v>107567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107567</v>
+        <v>107569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>137080259</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107569</v>
+        <v>107582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>137080259</v>
       </c>
       <c r="B4" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107582</v>
+        <v>107584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -947,11 +947,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1066,11 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Unger, Erik Ljungstrand, Eva Andersson</t>
+          <t>Eva Andersson, Erik Ljungstrand, Uno Unger</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107584</v>
+        <v>107588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>137080259</v>
       </c>
       <c r="B4" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Andersson, Erik Ljungstrand, Uno Unger</t>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107588</v>
+        <v>107609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107609</v>
+        <v>107610</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>137080259</v>
       </c>
       <c r="B4" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107610</v>
+        <v>107615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107615</v>
+        <v>107618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>137080259</v>
       </c>
       <c r="B4" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107618</v>
+        <v>107624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107624</v>
+        <v>107625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107625</v>
+        <v>107637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107637</v>
+        <v>107638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107638</v>
+        <v>107641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Unger, Erik Ljungstrand, Eva Andersson</t>
+          <t>Eva Andersson, Erik Ljungstrand, Uno Unger</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/S 611-2024 artfynd.xlsx
+++ b/artfynd/S 611-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>137080259</v>
       </c>
       <c r="B4" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Andersson, Erik Ljungstrand, Uno Unger</t>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
         <v>137078080</v>
       </c>
       <c r="B5" t="n">
-        <v>107641</v>
+        <v>107647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
